--- a/MATRIZ_CAMBIOS_PARAMETROS_LIMPIO.xlsx
+++ b/MATRIZ_CAMBIOS_PARAMETROS_LIMPIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8a3802af127234b/Documentos/GitHub/sicetac-api/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{491D5EEB-B188-4C06-B1EA-6F9D7B88381D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{320B4370-89EA-416D-98D0-8181C2B69312}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{491D5EEB-B188-4C06-B1EA-6F9D7B88381D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80EB8BF0-0ACC-4CC3-9AC4-E97F8B26802C}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -670,7 +670,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
@@ -680,7 +680,7 @@
       </c>
       <c r="D2" t="str">
         <f>+A2&amp;B2</f>
-        <v>202510C278</v>
+        <v>202512C278</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -755,15 +755,15 @@
         <v>11.03</v>
       </c>
       <c r="AC2">
-        <v>620.59309699999994</v>
+        <v>621.19079520265984</v>
       </c>
       <c r="AD2">
-        <v>620.59309689999998</v>
+        <v>621.19079520265984</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
@@ -773,7 +773,7 @@
       </c>
       <c r="D3" t="str">
         <f t="shared" ref="D3:D10" si="0">+A3&amp;B3</f>
-        <v>202510C289</v>
+        <v>202512C289</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -848,15 +848,15 @@
         <v>10.31</v>
       </c>
       <c r="AC3">
-        <v>641.06369700000005</v>
+        <v>641.68019711842942</v>
       </c>
       <c r="AD3">
-        <v>641.06369740000002</v>
+        <v>641.68019711842942</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B4" t="s">
         <v>29</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="D4" t="str">
         <f t="shared" si="0"/>
-        <v>202510C2910</v>
+        <v>202512C2910</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -941,15 +941,15 @@
         <v>9.6</v>
       </c>
       <c r="AC4">
-        <v>653.52820199999996</v>
+        <v>654.13520226409128</v>
       </c>
       <c r="AD4">
-        <v>653.52820220000001</v>
+        <v>654.13520226409128</v>
       </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
-        <v>202510C2M10</v>
+        <v>202512C2M10</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1034,15 +1034,15 @@
         <v>11.93</v>
       </c>
       <c r="AC5">
-        <v>753.43199800000002</v>
+        <v>753.87139803673222</v>
       </c>
       <c r="AD5">
-        <v>753.43199809999999</v>
+        <v>753.87139803673222</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v>202510C3</v>
+        <v>202512C3</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1127,15 +1127,15 @@
         <v>7.11</v>
       </c>
       <c r="AC6">
-        <v>1004.7681</v>
+        <v>1004.3210002374922</v>
       </c>
       <c r="AD6">
-        <v>1004.768099</v>
+        <v>1004.3210002374922</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
-        <v>202510C2S2</v>
+        <v>202512C2S2</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1220,15 +1220,15 @@
         <v>7.74</v>
       </c>
       <c r="AC7">
-        <v>1043.3551</v>
+        <v>1044.1863026440785</v>
       </c>
       <c r="AD7">
-        <v>1043.3551</v>
+        <v>1044.1863026440785</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
-        <v>202510C2S3</v>
+        <v>202512C2S3</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1313,15 +1313,15 @@
         <v>7.74</v>
       </c>
       <c r="AC8">
-        <v>1133.9996000000001</v>
+        <v>1133.4106040215327</v>
       </c>
       <c r="AD8">
-        <v>1133.9996040000001</v>
+        <v>1133.4106040215327</v>
       </c>
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
-        <v>202510C3S2</v>
+        <v>202512C3S2</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1406,15 +1406,15 @@
         <v>5.22</v>
       </c>
       <c r="AC9">
-        <v>1299.6695</v>
+        <v>1299.3439973875873</v>
       </c>
       <c r="AD9">
-        <v>1299.6695</v>
+        <v>1299.3439973875873</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>202510</v>
+        <v>202512</v>
       </c>
       <c r="B10" t="s">
         <v>35</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
-        <v>202510C3S3</v>
+        <v>202512C3S3</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1499,10 +1499,10 @@
         <v>4.97</v>
       </c>
       <c r="AC10">
-        <v>1565.3315</v>
+        <v>1564.8375949968336</v>
       </c>
       <c r="AD10">
-        <v>1565.3314989999999</v>
+        <v>1564.8375949968336</v>
       </c>
     </row>
   </sheetData>

--- a/MATRIZ_CAMBIOS_PARAMETROS_LIMPIO.xlsx
+++ b/MATRIZ_CAMBIOS_PARAMETROS_LIMPIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8a3802af127234b/Documentos/GitHub/sicetac-api/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{491D5EEB-B188-4C06-B1EA-6F9D7B88381D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80EB8BF0-0ACC-4CC3-9AC4-E97F8B26802C}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{491D5EEB-B188-4C06-B1EA-6F9D7B88381D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4D55029-C704-4015-9F10-FA1922C54B41}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -670,7 +670,7 @@
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
@@ -680,7 +680,7 @@
       </c>
       <c r="D2" t="str">
         <f>+A2&amp;B2</f>
-        <v>202512C278</v>
+        <v>202601C278</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>288</v>
       </c>
       <c r="G2">
-        <v>11076</v>
+        <v>11176</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B3" t="s">
         <v>28</v>
@@ -773,7 +773,7 @@
       </c>
       <c r="D3" t="str">
         <f t="shared" ref="D3:D10" si="0">+A3&amp;B3</f>
-        <v>202512C289</v>
+        <v>202601C289</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>288</v>
       </c>
       <c r="G3">
-        <v>11076</v>
+        <v>11176</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B4" t="s">
         <v>29</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="D4" t="str">
         <f t="shared" si="0"/>
-        <v>202512C2910</v>
+        <v>202601C2910</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>288</v>
       </c>
       <c r="G4">
-        <v>11076</v>
+        <v>11176</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -949,7 +949,7 @@
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B5" t="s">
         <v>30</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
-        <v>202512C2M10</v>
+        <v>202601C2M10</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -968,7 +968,7 @@
         <v>288</v>
       </c>
       <c r="G5">
-        <v>11076</v>
+        <v>11176</v>
       </c>
       <c r="H5">
         <v>9</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
-        <v>202512C3</v>
+        <v>202601C3</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1061,7 +1061,7 @@
         <v>288</v>
       </c>
       <c r="G6">
-        <v>11076</v>
+        <v>11176</v>
       </c>
       <c r="H6">
         <v>16</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
-        <v>202512C2S2</v>
+        <v>202601C2S2</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>288</v>
       </c>
       <c r="G7">
-        <v>11076</v>
+        <v>11176</v>
       </c>
       <c r="H7">
         <v>22</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B8" t="s">
         <v>33</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
-        <v>202512C2S3</v>
+        <v>202601C2S3</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>288</v>
       </c>
       <c r="G8">
-        <v>11076</v>
+        <v>11176</v>
       </c>
       <c r="H8">
         <v>27</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B9" t="s">
         <v>34</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
-        <v>202512C3S2</v>
+        <v>202601C3S2</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1340,7 +1340,7 @@
         <v>288</v>
       </c>
       <c r="G9">
-        <v>11076</v>
+        <v>11176</v>
       </c>
       <c r="H9">
         <v>31</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10">
-        <v>202512</v>
+        <v>202601</v>
       </c>
       <c r="B10" t="s">
         <v>35</v>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
-        <v>202512C3S3</v>
+        <v>202601C3S3</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1433,7 +1433,7 @@
         <v>288</v>
       </c>
       <c r="G10">
-        <v>11076</v>
+        <v>11176</v>
       </c>
       <c r="H10">
         <v>34</v>

--- a/MATRIZ_CAMBIOS_PARAMETROS_LIMPIO.xlsx
+++ b/MATRIZ_CAMBIOS_PARAMETROS_LIMPIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8a3802af127234b/Documentos/GitHub/sicetac-api/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{491D5EEB-B188-4C06-B1EA-6F9D7B88381D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4D55029-C704-4015-9F10-FA1922C54B41}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{491D5EEB-B188-4C06-B1EA-6F9D7B88381D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2624B587-49DC-4F50-AF24-F03031035C3C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>TIPO CONSOLIDADO</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>MES</t>
+  </si>
+  <si>
+    <t>V3</t>
   </si>
 </sst>
 </file>
@@ -568,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
@@ -1505,6 +1508,936 @@
         <v>1564.8375949968336</v>
       </c>
     </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>202602</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="str">
+        <f>+A11&amp;B11</f>
+        <v>202602C278</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>288</v>
+      </c>
+      <c r="G11">
+        <v>11276</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>62</v>
+      </c>
+      <c r="J11">
+        <v>50</v>
+      </c>
+      <c r="K11">
+        <v>25</v>
+      </c>
+      <c r="L11">
+        <v>25</v>
+      </c>
+      <c r="M11">
+        <v>10</v>
+      </c>
+      <c r="N11">
+        <v>74.7</v>
+      </c>
+      <c r="O11">
+        <v>62.25</v>
+      </c>
+      <c r="P11">
+        <v>31.13</v>
+      </c>
+      <c r="Q11">
+        <v>31.13</v>
+      </c>
+      <c r="R11">
+        <v>12.45</v>
+      </c>
+      <c r="S11">
+        <v>19</v>
+      </c>
+      <c r="T11">
+        <v>14.2</v>
+      </c>
+      <c r="U11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="V11">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="W11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X11">
+        <v>48.44</v>
+      </c>
+      <c r="Y11">
+        <v>36.21</v>
+      </c>
+      <c r="Z11">
+        <v>23.45</v>
+      </c>
+      <c r="AA11">
+        <v>23.45</v>
+      </c>
+      <c r="AB11">
+        <v>11.72</v>
+      </c>
+      <c r="AC11">
+        <v>625.48080272324262</v>
+      </c>
+      <c r="AD11">
+        <v>625.48080272324262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>202602</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="str">
+        <f>+A12&amp;B12</f>
+        <v>202602C289</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>288</v>
+      </c>
+      <c r="G12">
+        <v>11276</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <v>62</v>
+      </c>
+      <c r="J12">
+        <v>50</v>
+      </c>
+      <c r="K12">
+        <v>25</v>
+      </c>
+      <c r="L12">
+        <v>25</v>
+      </c>
+      <c r="M12">
+        <v>10</v>
+      </c>
+      <c r="N12">
+        <v>74.7</v>
+      </c>
+      <c r="O12">
+        <v>62.25</v>
+      </c>
+      <c r="P12">
+        <v>31.13</v>
+      </c>
+      <c r="Q12">
+        <v>31.13</v>
+      </c>
+      <c r="R12">
+        <v>12.45</v>
+      </c>
+      <c r="S12">
+        <v>18</v>
+      </c>
+      <c r="T12">
+        <v>13.7</v>
+      </c>
+      <c r="U12">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="V12">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="W12">
+        <v>4.3</v>
+      </c>
+      <c r="X12">
+        <v>45.89</v>
+      </c>
+      <c r="Y12">
+        <v>34.93</v>
+      </c>
+      <c r="Z12">
+        <v>22.17</v>
+      </c>
+      <c r="AA12">
+        <v>22.17</v>
+      </c>
+      <c r="AB12">
+        <v>10.96</v>
+      </c>
+      <c r="AC12">
+        <v>645.97020463901208</v>
+      </c>
+      <c r="AD12">
+        <v>645.97020463901208</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>202602</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:D20" si="1">+A13&amp;B13</f>
+        <v>202602C2910</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>288</v>
+      </c>
+      <c r="G13">
+        <v>11276</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13">
+        <v>62</v>
+      </c>
+      <c r="J13">
+        <v>50</v>
+      </c>
+      <c r="K13">
+        <v>25</v>
+      </c>
+      <c r="L13">
+        <v>25</v>
+      </c>
+      <c r="M13">
+        <v>10</v>
+      </c>
+      <c r="N13">
+        <v>74.7</v>
+      </c>
+      <c r="O13">
+        <v>62.25</v>
+      </c>
+      <c r="P13">
+        <v>31.13</v>
+      </c>
+      <c r="Q13">
+        <v>31.13</v>
+      </c>
+      <c r="R13">
+        <v>12.45</v>
+      </c>
+      <c r="S13">
+        <v>17</v>
+      </c>
+      <c r="T13">
+        <v>13</v>
+      </c>
+      <c r="U13">
+        <v>8</v>
+      </c>
+      <c r="V13">
+        <v>8</v>
+      </c>
+      <c r="W13">
+        <v>4</v>
+      </c>
+      <c r="X13">
+        <v>43.34</v>
+      </c>
+      <c r="Y13">
+        <v>33.15</v>
+      </c>
+      <c r="Z13">
+        <v>20.39</v>
+      </c>
+      <c r="AA13">
+        <v>20.39</v>
+      </c>
+      <c r="AB13">
+        <v>10.19</v>
+      </c>
+      <c r="AC13">
+        <v>658.42519988917047</v>
+      </c>
+      <c r="AD13">
+        <v>658.42519988917047</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>202602</v>
+      </c>
+      <c r="B14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14" t="str">
+        <f t="shared" si="1"/>
+        <v>202602C2M10</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>288</v>
+      </c>
+      <c r="G14">
+        <v>11276</v>
+      </c>
+      <c r="H14">
+        <v>9</v>
+      </c>
+      <c r="I14">
+        <v>60</v>
+      </c>
+      <c r="J14">
+        <v>35</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>20</v>
+      </c>
+      <c r="M14">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="N14">
+        <v>74.7</v>
+      </c>
+      <c r="O14">
+        <v>43.58</v>
+      </c>
+      <c r="P14">
+        <v>24.9</v>
+      </c>
+      <c r="Q14">
+        <v>24.9</v>
+      </c>
+      <c r="R14">
+        <v>11.89</v>
+      </c>
+      <c r="S14">
+        <v>12.7</v>
+      </c>
+      <c r="T14">
+        <v>10.01</v>
+      </c>
+      <c r="U14">
+        <v>7.81</v>
+      </c>
+      <c r="V14">
+        <v>7.81</v>
+      </c>
+      <c r="W14">
+        <v>4.97</v>
+      </c>
+      <c r="X14">
+        <v>32.380000000000003</v>
+      </c>
+      <c r="Y14">
+        <v>25.53</v>
+      </c>
+      <c r="Z14">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AA14">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AB14">
+        <v>12.67</v>
+      </c>
+      <c r="AC14">
+        <v>758.1613956618113</v>
+      </c>
+      <c r="AD14">
+        <v>758.1613956618113</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>202602</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="str">
+        <f t="shared" si="1"/>
+        <v>202602C3</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>288</v>
+      </c>
+      <c r="G15">
+        <v>11276</v>
+      </c>
+      <c r="H15">
+        <v>16</v>
+      </c>
+      <c r="I15">
+        <v>56.59</v>
+      </c>
+      <c r="J15">
+        <v>32.54</v>
+      </c>
+      <c r="K15">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="L15">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="M15">
+        <v>11.87</v>
+      </c>
+      <c r="N15">
+        <v>70.45</v>
+      </c>
+      <c r="O15">
+        <v>40.51</v>
+      </c>
+      <c r="P15">
+        <v>23.22</v>
+      </c>
+      <c r="Q15">
+        <v>23.22</v>
+      </c>
+      <c r="R15">
+        <v>14.78</v>
+      </c>
+      <c r="S15">
+        <v>8.06</v>
+      </c>
+      <c r="T15">
+        <v>6.22</v>
+      </c>
+      <c r="U15">
+        <v>4.66</v>
+      </c>
+      <c r="V15">
+        <v>4.66</v>
+      </c>
+      <c r="W15">
+        <v>2.97</v>
+      </c>
+      <c r="X15">
+        <v>20.55</v>
+      </c>
+      <c r="Y15">
+        <v>15.86</v>
+      </c>
+      <c r="Z15">
+        <v>11.88</v>
+      </c>
+      <c r="AA15">
+        <v>11.88</v>
+      </c>
+      <c r="AB15">
+        <v>7.56</v>
+      </c>
+      <c r="AC15">
+        <v>1023.3310045915136</v>
+      </c>
+      <c r="AD15">
+        <v>1023.3310045915136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>202602</v>
+      </c>
+      <c r="B16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" t="str">
+        <f t="shared" si="1"/>
+        <v>202602C2S2</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>288</v>
+      </c>
+      <c r="G16">
+        <v>11276</v>
+      </c>
+      <c r="H16">
+        <v>22</v>
+      </c>
+      <c r="I16">
+        <v>63.04</v>
+      </c>
+      <c r="J16">
+        <v>32.96</v>
+      </c>
+      <c r="K16">
+        <v>25.81</v>
+      </c>
+      <c r="L16">
+        <v>25.81</v>
+      </c>
+      <c r="M16">
+        <v>16.43</v>
+      </c>
+      <c r="N16">
+        <v>78.48</v>
+      </c>
+      <c r="O16">
+        <v>41.04</v>
+      </c>
+      <c r="P16">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="Q16">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="R16">
+        <v>20.46</v>
+      </c>
+      <c r="S16">
+        <v>8.76</v>
+      </c>
+      <c r="T16">
+        <v>6.76</v>
+      </c>
+      <c r="U16">
+        <v>5.07</v>
+      </c>
+      <c r="V16">
+        <v>5.07</v>
+      </c>
+      <c r="W16">
+        <v>3.23</v>
+      </c>
+      <c r="X16">
+        <v>22.33</v>
+      </c>
+      <c r="Y16">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="Z16">
+        <v>12.92</v>
+      </c>
+      <c r="AA16">
+        <v>12.92</v>
+      </c>
+      <c r="AB16">
+        <v>8.23</v>
+      </c>
+      <c r="AC16">
+        <v>1078.5162978942369</v>
+      </c>
+      <c r="AD16">
+        <v>1078.5162978942369</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>202602</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="str">
+        <f t="shared" si="1"/>
+        <v>202602C2S3</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>288</v>
+      </c>
+      <c r="G17">
+        <v>11276</v>
+      </c>
+      <c r="H17">
+        <v>27</v>
+      </c>
+      <c r="I17">
+        <v>63.04</v>
+      </c>
+      <c r="J17">
+        <v>32.96</v>
+      </c>
+      <c r="K17">
+        <v>25.81</v>
+      </c>
+      <c r="L17">
+        <v>25.81</v>
+      </c>
+      <c r="M17">
+        <v>16.43</v>
+      </c>
+      <c r="N17">
+        <v>78.48</v>
+      </c>
+      <c r="O17">
+        <v>41.04</v>
+      </c>
+      <c r="P17">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="Q17">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="R17">
+        <v>20.46</v>
+      </c>
+      <c r="S17">
+        <v>8.76</v>
+      </c>
+      <c r="T17">
+        <v>6.76</v>
+      </c>
+      <c r="U17">
+        <v>5.07</v>
+      </c>
+      <c r="V17">
+        <v>5.07</v>
+      </c>
+      <c r="W17">
+        <v>3.23</v>
+      </c>
+      <c r="X17">
+        <v>22.33</v>
+      </c>
+      <c r="Y17">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="Z17">
+        <v>12.92</v>
+      </c>
+      <c r="AA17">
+        <v>12.92</v>
+      </c>
+      <c r="AB17">
+        <v>8.23</v>
+      </c>
+      <c r="AC17">
+        <v>1171.6505996675112</v>
+      </c>
+      <c r="AD17">
+        <v>1171.6505996675112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>202602</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="str">
+        <f t="shared" si="1"/>
+        <v>202602C3S2</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>288</v>
+      </c>
+      <c r="G18">
+        <v>11276</v>
+      </c>
+      <c r="H18">
+        <v>31</v>
+      </c>
+      <c r="I18">
+        <v>56.25</v>
+      </c>
+      <c r="J18">
+        <v>33.130000000000003</v>
+      </c>
+      <c r="K18">
+        <v>23.57</v>
+      </c>
+      <c r="L18">
+        <v>23.57</v>
+      </c>
+      <c r="M18">
+        <v>15</v>
+      </c>
+      <c r="N18">
+        <v>70.03</v>
+      </c>
+      <c r="O18">
+        <v>41.25</v>
+      </c>
+      <c r="P18">
+        <v>29.34</v>
+      </c>
+      <c r="Q18">
+        <v>29.34</v>
+      </c>
+      <c r="R18">
+        <v>18.68</v>
+      </c>
+      <c r="S18">
+        <v>6.8</v>
+      </c>
+      <c r="T18">
+        <v>5.04</v>
+      </c>
+      <c r="U18">
+        <v>3.42</v>
+      </c>
+      <c r="V18">
+        <v>3.42</v>
+      </c>
+      <c r="W18">
+        <v>2.88</v>
+      </c>
+      <c r="X18">
+        <v>17.34</v>
+      </c>
+      <c r="Y18">
+        <v>12.85</v>
+      </c>
+      <c r="Z18">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="AA18">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="AB18">
+        <v>5.55</v>
+      </c>
+      <c r="AC18">
+        <v>1330.4539958043067</v>
+      </c>
+      <c r="AD18">
+        <v>1330.4539958043067</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>202602</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" t="str">
+        <f t="shared" si="1"/>
+        <v>202602C3S3</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>288</v>
+      </c>
+      <c r="G19">
+        <v>11276</v>
+      </c>
+      <c r="H19">
+        <v>34</v>
+      </c>
+      <c r="I19">
+        <v>56.25</v>
+      </c>
+      <c r="J19">
+        <v>33.130000000000003</v>
+      </c>
+      <c r="K19">
+        <v>23.57</v>
+      </c>
+      <c r="L19">
+        <v>23.57</v>
+      </c>
+      <c r="M19">
+        <v>15</v>
+      </c>
+      <c r="N19">
+        <v>70.03</v>
+      </c>
+      <c r="O19">
+        <v>41.25</v>
+      </c>
+      <c r="P19">
+        <v>29.34</v>
+      </c>
+      <c r="Q19">
+        <v>29.34</v>
+      </c>
+      <c r="R19">
+        <v>18.68</v>
+      </c>
+      <c r="S19">
+        <v>6.48</v>
+      </c>
+      <c r="T19">
+        <v>4.8</v>
+      </c>
+      <c r="U19">
+        <v>3.26</v>
+      </c>
+      <c r="V19">
+        <v>3.26</v>
+      </c>
+      <c r="W19">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="X19">
+        <v>16.52</v>
+      </c>
+      <c r="Y19">
+        <v>12.24</v>
+      </c>
+      <c r="Z19">
+        <v>8.31</v>
+      </c>
+      <c r="AA19">
+        <v>8.31</v>
+      </c>
+      <c r="AB19">
+        <v>5.28</v>
+      </c>
+      <c r="AC19">
+        <v>1583.7475953926537</v>
+      </c>
+      <c r="AD19">
+        <v>1583.7475953926537</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>202602</v>
+      </c>
+      <c r="B20" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" t="str">
+        <f t="shared" si="1"/>
+        <v>202602V3</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>288</v>
+      </c>
+      <c r="G20">
+        <v>11276</v>
+      </c>
+      <c r="H20">
+        <v>25</v>
+      </c>
+      <c r="I20">
+        <v>57.5</v>
+      </c>
+      <c r="J20">
+        <v>28.5</v>
+      </c>
+      <c r="K20">
+        <v>18.5</v>
+      </c>
+      <c r="L20">
+        <v>18.5</v>
+      </c>
+      <c r="M20">
+        <v>11.77</v>
+      </c>
+      <c r="N20">
+        <v>71.59</v>
+      </c>
+      <c r="O20">
+        <v>35.479999999999997</v>
+      </c>
+      <c r="P20">
+        <v>23.03</v>
+      </c>
+      <c r="Q20">
+        <v>23.03</v>
+      </c>
+      <c r="R20">
+        <v>14.66</v>
+      </c>
+      <c r="S20">
+        <v>9.27</v>
+      </c>
+      <c r="T20">
+        <v>8.4</v>
+      </c>
+      <c r="U20">
+        <v>7.1</v>
+      </c>
+      <c r="V20">
+        <v>7.1</v>
+      </c>
+      <c r="W20">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="X20">
+        <v>22.25</v>
+      </c>
+      <c r="Y20">
+        <v>20.16</v>
+      </c>
+      <c r="Z20">
+        <v>17.03</v>
+      </c>
+      <c r="AA20">
+        <v>17.03</v>
+      </c>
+      <c r="AB20">
+        <v>10.84</v>
+      </c>
+      <c r="AC20">
+        <v>1776.4791996516785</v>
+      </c>
+      <c r="AD20">
+        <v>1776.4791996516785</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/MATRIZ_CAMBIOS_PARAMETROS_LIMPIO.xlsx
+++ b/MATRIZ_CAMBIOS_PARAMETROS_LIMPIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8a3802af127234b/Documentos/GitHub/sicetac-api/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{491D5EEB-B188-4C06-B1EA-6F9D7B88381D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2624B587-49DC-4F50-AF24-F03031035C3C}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{491D5EEB-B188-4C06-B1EA-6F9D7B88381D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43B17371-6E6A-46C0-A5D2-376EDFFDB5FE}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22180" windowHeight="14140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="40">
   <si>
     <t>TIPO CONSOLIDADO</t>
   </si>
@@ -159,7 +159,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;\ #,##0.00;[Red]\-&quot;$&quot;\ #,##0.00"/>
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -238,7 +239,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="10">
+  <cellStyleXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -249,8 +250,9 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -258,11 +260,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="10">
+  <cellStyles count="11">
     <cellStyle name="Millares 2" xfId="8" xr:uid="{E0E47D35-1527-406E-BE09-D7A60204D652}"/>
     <cellStyle name="Millares 3" xfId="6" xr:uid="{3268FFD9-A980-444F-B6FE-F7CDBD3C43C7}"/>
     <cellStyle name="Millares 4" xfId="1" xr:uid="{DE7DF88D-3B5F-443C-88AE-35A555ADF5AF}"/>
+    <cellStyle name="Moneda" xfId="10" builtinId="4"/>
     <cellStyle name="Moneda 2" xfId="9" xr:uid="{31F44988-A427-4D47-AF42-B98055DEABC1}"/>
     <cellStyle name="Moneda 3" xfId="7" xr:uid="{7EC350E3-0BF9-47E8-9D26-0CB104258F24}"/>
     <cellStyle name="Moneda 4" xfId="2" xr:uid="{0745CBE7-541C-4DEF-B9D1-F195F0A1C621}"/>
@@ -571,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AN30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" bestFit="1" customWidth="1"/>
@@ -2066,7 +2071,7 @@
         <v>1078.5162978942369</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>202602</v>
       </c>
@@ -2159,7 +2164,7 @@
         <v>1171.6505996675112</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>202602</v>
       </c>
@@ -2252,7 +2257,7 @@
         <v>1330.4539958043067</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>202602</v>
       </c>
@@ -2345,7 +2350,7 @@
         <v>1583.7475953926537</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>202602</v>
       </c>
@@ -2437,6 +2442,1020 @@
       <c r="AD20">
         <v>1776.4791996516785</v>
       </c>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>202603</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21" t="str">
+        <f>+A21&amp;B21</f>
+        <v>202603C278</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>288</v>
+      </c>
+      <c r="G21">
+        <v>11276</v>
+      </c>
+      <c r="H21">
+        <v>4</v>
+      </c>
+      <c r="I21">
+        <v>62</v>
+      </c>
+      <c r="J21">
+        <v>50</v>
+      </c>
+      <c r="K21">
+        <v>25</v>
+      </c>
+      <c r="L21">
+        <v>25</v>
+      </c>
+      <c r="M21">
+        <v>10</v>
+      </c>
+      <c r="N21">
+        <v>74.7</v>
+      </c>
+      <c r="O21">
+        <v>62.25</v>
+      </c>
+      <c r="P21">
+        <v>31.13</v>
+      </c>
+      <c r="Q21">
+        <v>31.13</v>
+      </c>
+      <c r="R21">
+        <v>12.45</v>
+      </c>
+      <c r="S21">
+        <v>19</v>
+      </c>
+      <c r="T21">
+        <v>14.2</v>
+      </c>
+      <c r="U21">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="V21">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="W21">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="X21">
+        <v>48.44</v>
+      </c>
+      <c r="Y21">
+        <v>36.21</v>
+      </c>
+      <c r="Z21">
+        <v>23.45</v>
+      </c>
+      <c r="AA21">
+        <v>23.45</v>
+      </c>
+      <c r="AB21">
+        <v>11.72</v>
+      </c>
+      <c r="AC21">
+        <v>629.33569506016465</v>
+      </c>
+      <c r="AD21">
+        <v>629.33569506016465</v>
+      </c>
+      <c r="AE21" s="3"/>
+      <c r="AF21" s="3"/>
+      <c r="AG21" s="3"/>
+      <c r="AH21" s="3"/>
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="3"/>
+      <c r="AK21" s="3"/>
+      <c r="AM21" s="3"/>
+      <c r="AN21" s="3"/>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>202603</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22" t="str">
+        <f>+A22&amp;B22</f>
+        <v>202603C289</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>288</v>
+      </c>
+      <c r="G22">
+        <v>11276</v>
+      </c>
+      <c r="H22">
+        <v>5</v>
+      </c>
+      <c r="I22">
+        <v>62</v>
+      </c>
+      <c r="J22">
+        <v>50</v>
+      </c>
+      <c r="K22">
+        <v>25</v>
+      </c>
+      <c r="L22">
+        <v>25</v>
+      </c>
+      <c r="M22">
+        <v>10</v>
+      </c>
+      <c r="N22">
+        <v>74.7</v>
+      </c>
+      <c r="O22">
+        <v>62.25</v>
+      </c>
+      <c r="P22">
+        <v>31.13</v>
+      </c>
+      <c r="Q22">
+        <v>31.13</v>
+      </c>
+      <c r="R22">
+        <v>12.45</v>
+      </c>
+      <c r="S22">
+        <v>18</v>
+      </c>
+      <c r="T22">
+        <v>13.7</v>
+      </c>
+      <c r="U22">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="V22">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="W22">
+        <v>4.3</v>
+      </c>
+      <c r="X22">
+        <v>45.89</v>
+      </c>
+      <c r="Y22">
+        <v>34.93</v>
+      </c>
+      <c r="Z22">
+        <v>22.17</v>
+      </c>
+      <c r="AA22">
+        <v>22.17</v>
+      </c>
+      <c r="AB22">
+        <v>10.96</v>
+      </c>
+      <c r="AC22">
+        <v>649.91799596263456</v>
+      </c>
+      <c r="AD22">
+        <v>649.91799596263456</v>
+      </c>
+      <c r="AE22" s="3"/>
+      <c r="AF22" s="3"/>
+      <c r="AG22" s="3"/>
+      <c r="AH22" s="3"/>
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="3"/>
+      <c r="AK22" s="3"/>
+      <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>202603</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="str">
+        <f t="shared" ref="D23:D30" si="2">+A23&amp;B23</f>
+        <v>202603C2910</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>288</v>
+      </c>
+      <c r="G23">
+        <v>11276</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+      <c r="I23">
+        <v>62</v>
+      </c>
+      <c r="J23">
+        <v>50</v>
+      </c>
+      <c r="K23">
+        <v>25</v>
+      </c>
+      <c r="L23">
+        <v>25</v>
+      </c>
+      <c r="M23">
+        <v>10</v>
+      </c>
+      <c r="N23">
+        <v>74.7</v>
+      </c>
+      <c r="O23">
+        <v>62.25</v>
+      </c>
+      <c r="P23">
+        <v>31.13</v>
+      </c>
+      <c r="Q23">
+        <v>31.13</v>
+      </c>
+      <c r="R23">
+        <v>12.45</v>
+      </c>
+      <c r="S23">
+        <v>17</v>
+      </c>
+      <c r="T23">
+        <v>13</v>
+      </c>
+      <c r="U23">
+        <v>8</v>
+      </c>
+      <c r="V23">
+        <v>8</v>
+      </c>
+      <c r="W23">
+        <v>4</v>
+      </c>
+      <c r="X23">
+        <v>43.34</v>
+      </c>
+      <c r="Y23">
+        <v>33.15</v>
+      </c>
+      <c r="Z23">
+        <v>20.39</v>
+      </c>
+      <c r="AA23">
+        <v>20.39</v>
+      </c>
+      <c r="AB23">
+        <v>10.19</v>
+      </c>
+      <c r="AC23">
+        <v>662.36479773590884</v>
+      </c>
+      <c r="AD23">
+        <v>662.36479773590884</v>
+      </c>
+      <c r="AE23" s="3"/>
+      <c r="AF23" s="3"/>
+      <c r="AG23" s="3"/>
+      <c r="AH23" s="3"/>
+      <c r="AI23" s="3"/>
+      <c r="AJ23" s="3"/>
+      <c r="AK23" s="3"/>
+      <c r="AM23" s="3"/>
+      <c r="AN23" s="3"/>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A24">
+        <v>202603</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24" t="str">
+        <f t="shared" si="2"/>
+        <v>202603C2M10</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>288</v>
+      </c>
+      <c r="G24">
+        <v>11276</v>
+      </c>
+      <c r="H24">
+        <v>9</v>
+      </c>
+      <c r="I24">
+        <v>60</v>
+      </c>
+      <c r="J24">
+        <v>35</v>
+      </c>
+      <c r="K24">
+        <v>20</v>
+      </c>
+      <c r="L24">
+        <v>20</v>
+      </c>
+      <c r="M24">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="N24">
+        <v>74.7</v>
+      </c>
+      <c r="O24">
+        <v>43.58</v>
+      </c>
+      <c r="P24">
+        <v>24.9</v>
+      </c>
+      <c r="Q24">
+        <v>24.9</v>
+      </c>
+      <c r="R24">
+        <v>11.89</v>
+      </c>
+      <c r="S24">
+        <v>12.7</v>
+      </c>
+      <c r="T24">
+        <v>10.01</v>
+      </c>
+      <c r="U24">
+        <v>7.81</v>
+      </c>
+      <c r="V24">
+        <v>7.81</v>
+      </c>
+      <c r="W24">
+        <v>4.97</v>
+      </c>
+      <c r="X24">
+        <v>32.380000000000003</v>
+      </c>
+      <c r="Y24">
+        <v>25.53</v>
+      </c>
+      <c r="Z24">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AA24">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="AB24">
+        <v>12.67</v>
+      </c>
+      <c r="AC24">
+        <v>761.77499604179866</v>
+      </c>
+      <c r="AD24">
+        <v>761.77499604179866</v>
+      </c>
+      <c r="AE24" s="3"/>
+      <c r="AF24" s="3"/>
+      <c r="AG24" s="3"/>
+      <c r="AH24" s="3"/>
+      <c r="AI24" s="3"/>
+      <c r="AJ24" s="3"/>
+      <c r="AK24" s="3"/>
+      <c r="AM24" s="3"/>
+      <c r="AN24" s="3"/>
+    </row>
+    <row r="25" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>202603</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+      <c r="D25" t="str">
+        <f t="shared" si="2"/>
+        <v>202603C3</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>288</v>
+      </c>
+      <c r="G25">
+        <v>11276</v>
+      </c>
+      <c r="H25">
+        <v>16</v>
+      </c>
+      <c r="I25">
+        <v>56.59</v>
+      </c>
+      <c r="J25">
+        <v>32.54</v>
+      </c>
+      <c r="K25">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="L25">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="M25">
+        <v>11.87</v>
+      </c>
+      <c r="N25">
+        <v>70.45</v>
+      </c>
+      <c r="O25">
+        <v>40.51</v>
+      </c>
+      <c r="P25">
+        <v>23.22</v>
+      </c>
+      <c r="Q25">
+        <v>23.22</v>
+      </c>
+      <c r="R25">
+        <v>14.78</v>
+      </c>
+      <c r="S25">
+        <v>8.06</v>
+      </c>
+      <c r="T25">
+        <v>6.22</v>
+      </c>
+      <c r="U25">
+        <v>4.66</v>
+      </c>
+      <c r="V25">
+        <v>4.66</v>
+      </c>
+      <c r="W25">
+        <v>2.97</v>
+      </c>
+      <c r="X25">
+        <v>20.55</v>
+      </c>
+      <c r="Y25">
+        <v>15.86</v>
+      </c>
+      <c r="Z25">
+        <v>11.88</v>
+      </c>
+      <c r="AA25">
+        <v>11.88</v>
+      </c>
+      <c r="AB25">
+        <v>7.56</v>
+      </c>
+      <c r="AC25">
+        <v>1027.7264981792275</v>
+      </c>
+      <c r="AD25">
+        <v>1027.7264981792275</v>
+      </c>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="3"/>
+      <c r="AK25" s="3"/>
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+    </row>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>202603</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="str">
+        <f t="shared" si="2"/>
+        <v>202603C2S2</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>288</v>
+      </c>
+      <c r="G26">
+        <v>11276</v>
+      </c>
+      <c r="H26">
+        <v>22</v>
+      </c>
+      <c r="I26">
+        <v>63.04</v>
+      </c>
+      <c r="J26">
+        <v>32.96</v>
+      </c>
+      <c r="K26">
+        <v>25.81</v>
+      </c>
+      <c r="L26">
+        <v>25.81</v>
+      </c>
+      <c r="M26">
+        <v>16.43</v>
+      </c>
+      <c r="N26">
+        <v>78.48</v>
+      </c>
+      <c r="O26">
+        <v>41.04</v>
+      </c>
+      <c r="P26">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="Q26">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="R26">
+        <v>20.46</v>
+      </c>
+      <c r="S26">
+        <v>8.76</v>
+      </c>
+      <c r="T26">
+        <v>6.76</v>
+      </c>
+      <c r="U26">
+        <v>5.07</v>
+      </c>
+      <c r="V26">
+        <v>5.07</v>
+      </c>
+      <c r="W26">
+        <v>3.23</v>
+      </c>
+      <c r="X26">
+        <v>22.33</v>
+      </c>
+      <c r="Y26">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="Z26">
+        <v>12.92</v>
+      </c>
+      <c r="AA26">
+        <v>12.92</v>
+      </c>
+      <c r="AB26">
+        <v>8.23</v>
+      </c>
+      <c r="AC26">
+        <v>1081.3162998733376</v>
+      </c>
+      <c r="AD26">
+        <v>1081.3162998733376</v>
+      </c>
+      <c r="AE26" s="3"/>
+      <c r="AF26" s="3"/>
+      <c r="AG26" s="3"/>
+      <c r="AH26" s="3"/>
+      <c r="AI26" s="3"/>
+      <c r="AJ26" s="3"/>
+      <c r="AK26" s="3"/>
+      <c r="AM26" s="3"/>
+      <c r="AN26" s="3"/>
+    </row>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>202603</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="2"/>
+        <v>202603C2S3</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>288</v>
+      </c>
+      <c r="G27">
+        <v>11276</v>
+      </c>
+      <c r="H27">
+        <v>27</v>
+      </c>
+      <c r="I27">
+        <v>63.04</v>
+      </c>
+      <c r="J27">
+        <v>32.96</v>
+      </c>
+      <c r="K27">
+        <v>25.81</v>
+      </c>
+      <c r="L27">
+        <v>25.81</v>
+      </c>
+      <c r="M27">
+        <v>16.43</v>
+      </c>
+      <c r="N27">
+        <v>78.48</v>
+      </c>
+      <c r="O27">
+        <v>41.04</v>
+      </c>
+      <c r="P27">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="Q27">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="R27">
+        <v>20.46</v>
+      </c>
+      <c r="S27">
+        <v>8.76</v>
+      </c>
+      <c r="T27">
+        <v>6.76</v>
+      </c>
+      <c r="U27">
+        <v>5.07</v>
+      </c>
+      <c r="V27">
+        <v>5.07</v>
+      </c>
+      <c r="W27">
+        <v>3.23</v>
+      </c>
+      <c r="X27">
+        <v>22.33</v>
+      </c>
+      <c r="Y27">
+        <v>17.239999999999998</v>
+      </c>
+      <c r="Z27">
+        <v>12.92</v>
+      </c>
+      <c r="AA27">
+        <v>12.92</v>
+      </c>
+      <c r="AB27">
+        <v>8.23</v>
+      </c>
+      <c r="AC27">
+        <v>1174.6818001899937</v>
+      </c>
+      <c r="AD27">
+        <v>1174.6818001899937</v>
+      </c>
+      <c r="AE27" s="3"/>
+      <c r="AF27" s="3"/>
+      <c r="AG27" s="3"/>
+      <c r="AH27" s="3"/>
+      <c r="AI27" s="3"/>
+      <c r="AJ27" s="3"/>
+      <c r="AK27" s="3"/>
+      <c r="AM27" s="3"/>
+      <c r="AN27" s="3"/>
+    </row>
+    <row r="28" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>202603</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="2"/>
+        <v>202603C3S2</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>288</v>
+      </c>
+      <c r="G28">
+        <v>11276</v>
+      </c>
+      <c r="H28">
+        <v>31</v>
+      </c>
+      <c r="I28">
+        <v>56.25</v>
+      </c>
+      <c r="J28">
+        <v>33.130000000000003</v>
+      </c>
+      <c r="K28">
+        <v>23.57</v>
+      </c>
+      <c r="L28">
+        <v>23.57</v>
+      </c>
+      <c r="M28">
+        <v>15</v>
+      </c>
+      <c r="N28">
+        <v>70.03</v>
+      </c>
+      <c r="O28">
+        <v>41.25</v>
+      </c>
+      <c r="P28">
+        <v>29.34</v>
+      </c>
+      <c r="Q28">
+        <v>29.34</v>
+      </c>
+      <c r="R28">
+        <v>18.68</v>
+      </c>
+      <c r="S28">
+        <v>6.8</v>
+      </c>
+      <c r="T28">
+        <v>5.04</v>
+      </c>
+      <c r="U28">
+        <v>3.42</v>
+      </c>
+      <c r="V28">
+        <v>3.42</v>
+      </c>
+      <c r="W28">
+        <v>2.88</v>
+      </c>
+      <c r="X28">
+        <v>17.34</v>
+      </c>
+      <c r="Y28">
+        <v>12.85</v>
+      </c>
+      <c r="Z28">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="AA28">
+        <v>8.7200000000000006</v>
+      </c>
+      <c r="AB28">
+        <v>5.55</v>
+      </c>
+      <c r="AC28">
+        <v>1334.2327026599114</v>
+      </c>
+      <c r="AD28">
+        <v>1334.2327026599114</v>
+      </c>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="3"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="3"/>
+      <c r="AK28" s="3"/>
+      <c r="AM28" s="3"/>
+      <c r="AN28" s="3"/>
+    </row>
+    <row r="29" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>202603</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="2"/>
+        <v>202603C3S3</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>288</v>
+      </c>
+      <c r="G29">
+        <v>11276</v>
+      </c>
+      <c r="H29">
+        <v>34</v>
+      </c>
+      <c r="I29">
+        <v>56.25</v>
+      </c>
+      <c r="J29">
+        <v>33.130000000000003</v>
+      </c>
+      <c r="K29">
+        <v>23.57</v>
+      </c>
+      <c r="L29">
+        <v>23.57</v>
+      </c>
+      <c r="M29">
+        <v>15</v>
+      </c>
+      <c r="N29">
+        <v>70.03</v>
+      </c>
+      <c r="O29">
+        <v>41.25</v>
+      </c>
+      <c r="P29">
+        <v>29.34</v>
+      </c>
+      <c r="Q29">
+        <v>29.34</v>
+      </c>
+      <c r="R29">
+        <v>18.68</v>
+      </c>
+      <c r="S29">
+        <v>6.48</v>
+      </c>
+      <c r="T29">
+        <v>4.8</v>
+      </c>
+      <c r="U29">
+        <v>3.26</v>
+      </c>
+      <c r="V29">
+        <v>3.26</v>
+      </c>
+      <c r="W29">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="X29">
+        <v>16.52</v>
+      </c>
+      <c r="Y29">
+        <v>12.24</v>
+      </c>
+      <c r="Z29">
+        <v>8.31</v>
+      </c>
+      <c r="AA29">
+        <v>8.31</v>
+      </c>
+      <c r="AB29">
+        <v>5.28</v>
+      </c>
+      <c r="AC29">
+        <v>1587.6381016466119</v>
+      </c>
+      <c r="AD29">
+        <v>1587.6381016466119</v>
+      </c>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="3"/>
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="3"/>
+      <c r="AK29" s="3"/>
+      <c r="AM29" s="3"/>
+      <c r="AN29" s="3"/>
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.35">
+      <c r="A30">
+        <v>202603</v>
+      </c>
+      <c r="B30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="2"/>
+        <v>202603V3</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>288</v>
+      </c>
+      <c r="G30">
+        <v>11276</v>
+      </c>
+      <c r="H30">
+        <v>25</v>
+      </c>
+      <c r="I30">
+        <v>57.5</v>
+      </c>
+      <c r="J30">
+        <v>28.5</v>
+      </c>
+      <c r="K30">
+        <v>18.5</v>
+      </c>
+      <c r="L30">
+        <v>18.5</v>
+      </c>
+      <c r="M30">
+        <v>11.77</v>
+      </c>
+      <c r="N30">
+        <v>71.59</v>
+      </c>
+      <c r="O30">
+        <v>35.479999999999997</v>
+      </c>
+      <c r="P30">
+        <v>23.03</v>
+      </c>
+      <c r="Q30">
+        <v>23.03</v>
+      </c>
+      <c r="R30">
+        <v>14.66</v>
+      </c>
+      <c r="S30">
+        <v>9.27</v>
+      </c>
+      <c r="T30">
+        <v>8.4</v>
+      </c>
+      <c r="U30">
+        <v>7.1</v>
+      </c>
+      <c r="V30">
+        <v>7.1</v>
+      </c>
+      <c r="W30">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="X30">
+        <v>22.25</v>
+      </c>
+      <c r="Y30">
+        <v>20.16</v>
+      </c>
+      <c r="Z30">
+        <v>17.03</v>
+      </c>
+      <c r="AA30">
+        <v>17.03</v>
+      </c>
+      <c r="AB30">
+        <v>10.84</v>
+      </c>
+      <c r="AC30">
+        <v>1791.6383985117166</v>
+      </c>
+      <c r="AD30">
+        <v>1791.6383985117166</v>
+      </c>
+      <c r="AE30" s="3"/>
+      <c r="AM30" s="4"/>
+      <c r="AN30" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
